--- a/data/klinieken.xlsx
+++ b/data/klinieken.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.4296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="3" min="1" max="1"/>
@@ -470,6 +470,26 @@
           <t>Volgorde</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Voor wie</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Wat verwachten</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Praktisch</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="23.65" customHeight="1" s="4">
       <c r="A2" s="6" t="inlineStr">
@@ -510,6 +530,26 @@
       <c r="H2" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Patiënten met luid snurken, vermoeden van slaapapneu, overmatige slaperigheid overdag, onrustige slaap, of onverklaarbare vermoeidheid. Ook voor chauffeurs en piloten die een medisch attest nodig hebben.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Na een consultatie met de slaapspecialist wordt u uitgenodigd voor een polysomnografie (slaapstudie). U slaapt één nacht in ons slaaplabo, waar sensoren uw ademhaling, hersengolven, hartritme en beenbewegingen registreren. Het onderzoek is pijnloos. Resultaten worden doorgaans binnen 2 weken besproken.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Dr. V. Adam en Dr. H. Nguyen (longartsen-slaapspecialisten), slaaptechnologen, gespecialiseerde verpleegkundigen.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Slaaplabo op campus Aalst — Moorselbaan. Afspraak via het secretariaat. Breng comfortabele slaapkledij mee. Vermijd cafeïne op de dag van het onderzoek.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="6" t="inlineStr">
@@ -550,6 +590,26 @@
       <c r="H3" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Iedereen die wil stoppen met roken — of u nu 5 of 40 jaar rookt. Ook voor e-sigaretgebruikers die willen afbouwen. Speciale aandacht voor patiënten met COPD, astma, longkanker of hart- en vaatziekten.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Een persoonlijk intakegesprek waarin we uw rookgewoonten en motivatie bespreken. Daarna een traject op maat: nikotinevervangers, medicatie, en regelmatige motivatiegesprekken. Gemiddeld 6 à 8 sessies over 3 maanden. Terugbetalingsmogelijkheden via het ziekenfonds.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Erkende tabakologen: gespecialiseerde verpleegkundigen en psychologen met extra opleiding in rookstopbegeleiding.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Beschikbaar op alle campussen. Contact: rookstopkliniek@azorg.be. Geen verwijsbrief nodig.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="6" t="inlineStr">
@@ -590,6 +650,26 @@
       <c r="H4" s="6" t="n">
         <v>3</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sporters (recreatief en competitief) die hun longfunctie en inspanningsvermogen willen laten testen. Patiënten met longaandoeningen die veilig willen sporten. Duikers die een medisch attest nodig hebben.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cardiopulmonaire inspanningstest (CPET) op de fiets: u fietst met toenemende weerstand terwijl we ademhaling, hartritme, bloeddruk en zuurstof meten. Voor duikers: aanvullend longfunctieonderzoek en specifieke duikmedische keuring. Resultaat en advies op maat.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Dr. H. Nguyen (longarts, sportarts, duikmedisch specialist).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Campus Aalst — Moorselbaan. Breng sportkleding en -schoenen mee. Eet licht 2 uur voor de test. Duur: circa 45 minuten.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.65" customHeight="1" s="4">
       <c r="A5" s="6" t="inlineStr">
@@ -630,6 +710,26 @@
       <c r="H5" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Patiënten met COPD, astma, longfibrose, longkanker (voor/na behandeling), post-COVID met aanhoudende klachten, of andere chronische longziekten die leiden tot verminderde conditie en kortademigheid.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Een multidisciplinair programma van 3 tot 6 maanden: 2 à 3 sessies per week met inspanningstraining, ademhalingsoefeningen, voorlichting over uw ziekte, voedingsadvies en psychologische ondersteuning. Voor en na het programma meten we uw vooruitgang via een inspanningstest.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Dr. An Pletinckx (longarts-revalidatiespecialist), kinesisten gespecialiseerd in respiratoire revalidatie, diëtisten, psychologen, maatschappelijk werkers.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Campus Aalst — Moorselbaan. Verwijzing door longarts of huisarts. Grotendeels terugbetaald door het ziekenfonds. Breng sportkleding mee.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="6" t="inlineStr">
@@ -670,6 +770,26 @@
       <c r="H6" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Alle patiënten met (vermoeden van) longkanker, longknobbeljes ontdekt op CT-scan, of mesothelioom. Elke patiënt wordt persoonlijk besproken — ook als u verwezen wordt door een ander ziekenhuis.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Na de diagnose bespreken we uw dossier in het wekelijks Multidisciplinair Oncologisch Consult (MOC). Daar zitten longartsen, thoraxchirurgen, medisch oncologen, radiotherapeuten, radiologen en pathologen samen. U krijgt een behandelplan op maat, met uitleg door uw longarts. Wij begeleiden u door het volledige traject.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Longartsen, thoraxchirurgen, medisch oncologen, radiotherapeuten, radiologen, patholoog-anatomen, oncologieverpleegkundigen, psychologen, palliatief team.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MOC vindt wekelijks plaats op campus Aalst — Moorselbaan. Uw longarts meldt uw dossier aan. Resultaat wordt doorgaans binnen enkele dagen met u besproken.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="4">
       <c r="A7" s="6" t="inlineStr">
@@ -709,6 +829,26 @@
       </c>
       <c r="H7" s="6" t="n">
         <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Patiënten die in aanmerking komen voor klinische studies naar nieuwe behandelingen voor astma, COPD, longkanker, longfibrose of slaapapneu. Deelname is altijd vrijwillig en wordt uitvoerig besproken.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Uw longarts bespreekt de mogelijkheid van deelname aan een studie. U ontvangt gedetailleerde informatie en ondertekent een toestemmingsformulier. Tijdens de studie wordt u intensief opgevolgd met extra consultaties en onderzoeken. U kunt op elk moment stoppen.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Studiecoördinatoren (verpleegkundigen), longartsen-onderzoekers, data managers. Verbonden aan de Universiteit Gent als academisch opleidingscentrum.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Studies lopen op campus Aalst — Moorselbaan. Vergoeding voor reiskosten mogelijk. Vraag uw longarts of er een lopende studie is voor uw aandoening.</t>
+        </is>
       </c>
     </row>
   </sheetData>
